--- a/Tanzania_Tourism_Companies _Dataset.xlsx
+++ b/Tanzania_Tourism_Companies _Dataset.xlsx
@@ -1,14 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\projects_portfolio\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3411A76A-0AA8-49B1-B5CA-3C15822DB0FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Chart1" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="Sheet2" sheetId="3" r:id="rId7"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -1164,72 +1171,73 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="12">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF434343"/>
       <name val="Arial"/>
     </font>
     <font>
       <u/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF434343"/>
       <name val="Arial"/>
     </font>
     <font>
       <u/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
       <u/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
       <u/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF434343"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
       <u/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF434343"/>
       <name val="Arial"/>
     </font>
     <font>
       <u/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF434343"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF1D293F"/>
       <name val="Arial"/>
     </font>
     <font>
       <u/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF434343"/>
       <name val="Arial"/>
     </font>
@@ -1239,7 +1247,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1255,7 +1263,13 @@
     </fill>
   </fills>
   <borders count="10">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF284E3F"/>
@@ -1269,6 +1283,7 @@
       <bottom style="thin">
         <color rgb="FFFFFFFF"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1283,6 +1298,7 @@
       <bottom style="thin">
         <color rgb="FFFFFFFF"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1297,6 +1313,7 @@
       <bottom style="thin">
         <color rgb="FFFFFFFF"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1311,6 +1328,7 @@
       <bottom style="thin">
         <color rgb="FFF6F8F9"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1325,6 +1343,7 @@
       <bottom style="thin">
         <color rgb="FFF6F8F9"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1339,6 +1358,7 @@
       <bottom style="thin">
         <color rgb="FFF6F8F9"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1353,6 +1373,7 @@
       <bottom style="thin">
         <color rgb="FF284E3F"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1367,6 +1388,7 @@
       <bottom style="thin">
         <color rgb="FF284E3F"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1381,171 +1403,54 @@
       <bottom style="thin">
         <color rgb="FF284E3F"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="26">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf quotePrefix="1" borderId="2" fillId="2" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="3" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="5" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="5" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="5" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="5" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf quotePrefix="1" borderId="5" fillId="3" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="6" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="3" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="5" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="5" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="5" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="6" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="6" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="3" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="6" fillId="3" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="7" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="8" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="8" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="8" fillId="3" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="8" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf quotePrefix="1" borderId="8" fillId="3" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="9" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF00AAFF"/>
-          <bgColor rgb="FF00AAFF"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF6F8F9"/>
-          <bgColor rgb="FFF6F8F9"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <border>
         <left style="thin">
@@ -1562,217 +1467,66 @@
         </bottom>
       </border>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF00AAFF"/>
+          <bgColor rgb="FF00AAFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle count="4" pivot="0" name="Sheet1-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
-      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
+    <tableStyle name="Sheet1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+      <tableStyleElement type="wholeTable" size="0" dxfId="0"/>
+      <tableStyleElement type="headerRow" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="secondRowStripe" dxfId="1"/>
     </tableStyle>
   </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>523875</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="5715000" cy="3533775"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="134052097" name="Chart1" title="Chart">
-          <a:extLst>
-            <a:ext uri="GoogleSheetsCustomDataVersion1">
-              <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" pictureOfChart="1"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>285750</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="10077450" cy="6238875"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2048816983" name="Chart2" title="Chart">
-          <a:extLst>
-            <a:ext uri="GoogleSheetsCustomDataVersion1">
-              <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" pictureOfChart="1"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>219075</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="5715000" cy="3533775"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="91879347" name="Chart3" title="Chart">
-          <a:extLst>
-            <a:ext uri="GoogleSheetsCustomDataVersion1">
-              <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" pictureOfChart="1"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>847725</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="5715000" cy="3533775"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="1410796903" name="Chart4" title="Chart">
-          <a:extLst>
-            <a:ext uri="GoogleSheetsCustomDataVersion1">
-              <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" pictureOfChart="1"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="8610600" cy="6276975"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="234272014" name="Chart5" title="Chart">
-          <a:extLst>
-            <a:ext uri="GoogleSheetsCustomDataVersion1">
-              <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" pictureOfChart="1"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A1:K1" displayName="Tourism_companies" name="Tourism_companies" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tourism_companies" displayName="Tourism_companies" ref="A1:K1" headerRowCount="0">
   <tableColumns count="11">
-    <tableColumn name="Column1" id="1"/>
-    <tableColumn name="Column2" id="2"/>
-    <tableColumn name="Column3" id="3"/>
-    <tableColumn name="Column4" id="4"/>
-    <tableColumn name="Column5" id="5"/>
-    <tableColumn name="Column6" id="6"/>
-    <tableColumn name="Column7" id="7"/>
-    <tableColumn name="Column8" id="8"/>
-    <tableColumn name="Column9" id="9"/>
-    <tableColumn name="Column10" id="10"/>
-    <tableColumn name="Column11" id="11"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Column1"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Column2"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Column3"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Column4"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Column5"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Column6"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Column7"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Column8"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Column9"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Column10"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Column11"/>
   </tableColumns>
-  <tableStyleInfo name="Sheet1-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="Sheet1-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" headerRowCount="1"/>
@@ -1782,7 +1536,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1972,36 +1726,39 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="28.88"/>
-    <col customWidth="1" min="3" max="3" width="17.75"/>
-    <col customWidth="1" min="4" max="4" width="29.13"/>
-    <col customWidth="1" min="5" max="5" width="47.5"/>
-    <col customWidth="1" min="6" max="6" width="27.25"/>
-    <col customWidth="1" min="7" max="7" width="31.63"/>
-    <col customWidth="1" min="8" max="8" width="33.5"/>
-    <col customWidth="1" min="9" max="9" width="24.5"/>
-    <col customWidth="1" min="10" max="10" width="27.63"/>
-    <col customWidth="1" min="11" max="11" width="27.25"/>
+    <col min="2" max="2" width="28.90625" customWidth="1"/>
+    <col min="3" max="3" width="17.7265625" customWidth="1"/>
+    <col min="4" max="4" width="29.08984375" customWidth="1"/>
+    <col min="5" max="5" width="47.453125" customWidth="1"/>
+    <col min="6" max="6" width="27.26953125" customWidth="1"/>
+    <col min="7" max="7" width="31.6328125" customWidth="1"/>
+    <col min="8" max="8" width="33.453125" customWidth="1"/>
+    <col min="9" max="9" width="24.453125" customWidth="1"/>
+    <col min="10" max="10" width="27.6328125" customWidth="1"/>
+    <col min="11" max="11" width="29.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" customHeight="1">
+    <row r="1" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -2013,1867 +1770,1848 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="B2" s="5" t="s">
+    <row r="2" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="K2" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="11">
-        <v>2.0</v>
-      </c>
-      <c r="B3" s="12" t="s">
+    <row r="3" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A3" s="8">
+        <v>2</v>
+      </c>
+      <c r="B3" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="G3" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="15" t="s">
+      <c r="H3" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="16" t="s">
+      <c r="I3" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="12" t="s">
+      <c r="J3" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="K3" s="17" t="s">
+      <c r="K3" s="13" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="B4" s="5" t="s">
+    <row r="4" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="18" t="s">
+      <c r="G4" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K4" s="19" t="s">
+      <c r="K4" s="7" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="11">
-        <v>4.0</v>
-      </c>
-      <c r="B5" s="12" t="s">
+    <row r="5" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A5" s="8">
+        <v>4</v>
+      </c>
+      <c r="B5" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="20" t="s">
+      <c r="G5" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="H5" s="21" t="s">
+      <c r="H5" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="I5" s="22" t="s">
+      <c r="I5" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="J5" s="12" t="s">
+      <c r="J5" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="K5" s="17" t="s">
+      <c r="K5" s="13" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="B6" s="5" t="s">
+    <row r="6" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="G6" s="18" t="s">
+      <c r="G6" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="H6" s="23" t="s">
+      <c r="H6" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="I6" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="J6" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="K6" s="19" t="s">
+      <c r="K6" s="7" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="11">
-        <v>6.0</v>
-      </c>
-      <c r="B7" s="12" t="s">
+    <row r="7" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A7" s="8">
+        <v>6</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="G7" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="H7" s="24" t="s">
+      <c r="H7" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="I7" s="16" t="s">
+      <c r="I7" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="J7" s="12" t="s">
+      <c r="J7" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="K7" s="17" t="s">
+      <c r="K7" s="13" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4">
-        <v>7.0</v>
-      </c>
-      <c r="B8" s="5" t="s">
+    <row r="8" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="H8" s="23" t="s">
+      <c r="H8" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="I8" s="9" t="s">
+      <c r="I8" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="J8" s="5" t="s">
+      <c r="J8" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="K8" s="10" t="s">
+      <c r="K8" s="7" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="11">
-        <v>8.0</v>
-      </c>
-      <c r="B9" s="12" t="s">
+    <row r="9" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A9" s="8">
+        <v>8</v>
+      </c>
+      <c r="B9" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="F9" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="G9" s="20" t="s">
+      <c r="G9" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="H9" s="24" t="s">
+      <c r="H9" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="16" t="s">
+      <c r="I9" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="12" t="s">
+      <c r="J9" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="17" t="s">
+      <c r="K9" s="13" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4">
-        <v>9.0</v>
-      </c>
-      <c r="B10" s="5" t="s">
+    <row r="10" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="H10" s="25" t="s">
+      <c r="H10" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="I10" s="9" t="s">
+      <c r="I10" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="J10" s="5" t="s">
+      <c r="J10" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="K10" s="19" t="s">
+      <c r="K10" s="7" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="11">
-        <v>10.0</v>
-      </c>
-      <c r="B11" s="12" t="s">
+    <row r="11" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A11" s="8">
+        <v>10</v>
+      </c>
+      <c r="B11" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="E11" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="F11" s="13" t="s">
+      <c r="F11" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="G11" s="20" t="s">
+      <c r="G11" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="H11" s="21" t="s">
+      <c r="H11" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="I11" s="16" t="s">
+      <c r="I11" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="J11" s="12" t="s">
+      <c r="J11" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="K11" s="17" t="s">
+      <c r="K11" s="13" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4">
-        <v>11.0</v>
-      </c>
-      <c r="B12" s="5" t="s">
+    <row r="12" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="H12" s="23" t="s">
+      <c r="H12" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="I12" s="9" t="s">
+      <c r="I12" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="J12" s="5" t="s">
+      <c r="J12" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="K12" s="19" t="s">
+      <c r="K12" s="7" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="11">
-        <v>12.0</v>
-      </c>
-      <c r="B13" s="12" t="s">
+    <row r="13" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A13" s="8">
+        <v>12</v>
+      </c>
+      <c r="B13" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="F13" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="G13" s="20" t="s">
+      <c r="G13" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="H13" s="24" t="s">
+      <c r="H13" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="I13" s="16" t="s">
+      <c r="I13" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="J13" s="12" t="s">
+      <c r="J13" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="K13" s="17" t="s">
+      <c r="K13" s="13" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4">
-        <v>13.0</v>
-      </c>
-      <c r="B14" s="5" t="s">
+    <row r="14" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="G14" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="H14" s="23" t="s">
+      <c r="H14" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="I14" s="9" t="s">
+      <c r="I14" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="J14" s="5" t="s">
+      <c r="J14" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="K14" s="19" t="s">
+      <c r="K14" s="7" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="11">
-        <v>14.0</v>
-      </c>
-      <c r="B15" s="12" t="s">
+    <row r="15" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A15" s="8">
+        <v>14</v>
+      </c>
+      <c r="B15" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="F15" s="13" t="s">
+      <c r="F15" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="G15" s="20" t="s">
+      <c r="G15" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="H15" s="24" t="s">
+      <c r="H15" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="I15" s="16" t="s">
+      <c r="I15" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="J15" s="12" t="s">
+      <c r="J15" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="K15" s="26" t="s">
+      <c r="K15" s="13" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4">
-        <v>15.0</v>
-      </c>
-      <c r="B16" s="5" t="s">
+    <row r="16" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="F16" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="G16" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="H16" s="23" t="s">
+      <c r="H16" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="I16" s="9" t="s">
+      <c r="I16" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="J16" s="5" t="s">
+      <c r="J16" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="K16" s="19" t="s">
+      <c r="K16" s="7" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="11">
-        <v>16.0</v>
-      </c>
-      <c r="B17" s="12" t="s">
+    <row r="17" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A17" s="8">
+        <v>16</v>
+      </c>
+      <c r="B17" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E17" s="12" t="s">
+      <c r="E17" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="F17" s="12" t="s">
+      <c r="F17" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="G17" s="20" t="s">
+      <c r="G17" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="H17" s="24" t="s">
+      <c r="H17" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="I17" s="16" t="s">
+      <c r="I17" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="J17" s="12" t="s">
+      <c r="J17" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="K17" s="17" t="s">
+      <c r="K17" s="13" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4">
-        <v>17.0</v>
-      </c>
-      <c r="B18" s="5" t="s">
+    <row r="18" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="F18" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="G18" s="7" t="s">
+      <c r="G18" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="H18" s="23" t="s">
+      <c r="H18" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="I18" s="9" t="s">
+      <c r="I18" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J18" s="5" t="s">
+      <c r="J18" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="K18" s="19" t="s">
+      <c r="K18" s="7" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="11">
-        <v>18.0</v>
-      </c>
-      <c r="B19" s="12" t="s">
+    <row r="19" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A19" s="8">
+        <v>18</v>
+      </c>
+      <c r="B19" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="D19" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="E19" s="12" t="s">
+      <c r="E19" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="F19" s="13" t="s">
+      <c r="F19" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="G19" s="20" t="s">
+      <c r="G19" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="H19" s="21" t="s">
+      <c r="H19" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="I19" s="16" t="s">
+      <c r="I19" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="J19" s="12" t="s">
+      <c r="J19" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="K19" s="17" t="s">
+      <c r="K19" s="13" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4">
-        <v>19.0</v>
-      </c>
-      <c r="B20" s="5" t="s">
+    <row r="20" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <v>19</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="F20" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="G20" s="7" t="s">
+      <c r="G20" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="H20" s="23" t="s">
+      <c r="H20" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="I20" s="27" t="s">
+      <c r="I20" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="J20" s="5" t="s">
+      <c r="J20" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="K20" s="19" t="s">
+      <c r="K20" s="7" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="11">
-        <v>20.0</v>
-      </c>
-      <c r="B21" s="12" t="s">
+    <row r="21" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A21" s="8">
+        <v>20</v>
+      </c>
+      <c r="B21" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="D21" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="E21" s="12" t="s">
+      <c r="E21" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="F21" s="13" t="s">
+      <c r="F21" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="G21" s="20" t="s">
+      <c r="G21" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="H21" s="24" t="s">
+      <c r="H21" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="I21" s="16" t="s">
+      <c r="I21" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="J21" s="12" t="s">
+      <c r="J21" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="K21" s="17" t="s">
+      <c r="K21" s="13" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4">
-        <v>21.0</v>
-      </c>
-      <c r="B22" s="5" t="s">
+    <row r="22" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
+        <v>21</v>
+      </c>
+      <c r="B22" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D22" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="F22" s="6" t="s">
+      <c r="F22" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="G22" s="7" t="s">
+      <c r="G22" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="H22" s="25" t="s">
+      <c r="H22" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="I22" s="9" t="s">
+      <c r="I22" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="J22" s="5" t="s">
+      <c r="J22" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="K22" s="19" t="s">
+      <c r="K22" s="7" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="11">
-        <v>22.0</v>
-      </c>
-      <c r="B23" s="12" t="s">
+    <row r="23" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A23" s="8">
+        <v>22</v>
+      </c>
+      <c r="B23" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C23" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D23" s="13" t="s">
+      <c r="D23" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E23" s="12" t="s">
+      <c r="E23" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="F23" s="13" t="s">
+      <c r="F23" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="G23" s="20" t="s">
+      <c r="G23" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="H23" s="21" t="s">
+      <c r="H23" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="I23" s="27" t="s">
+      <c r="I23" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="J23" s="12" t="s">
+      <c r="J23" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="K23" s="17" t="s">
+      <c r="K23" s="13" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4">
-        <v>23.0</v>
-      </c>
-      <c r="B24" s="5" t="s">
+    <row r="24" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <v>23</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="D24" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="E24" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="F24" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="G24" s="7" t="s">
+      <c r="G24" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="H24" s="23" t="s">
+      <c r="H24" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="I24" s="9" t="s">
+      <c r="I24" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="J24" s="5" t="s">
+      <c r="J24" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="K24" s="19" t="s">
+      <c r="K24" s="7" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="11">
-        <v>24.0</v>
-      </c>
-      <c r="B25" s="12" t="s">
+    <row r="25" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A25" s="8">
+        <v>24</v>
+      </c>
+      <c r="B25" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="C25" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D25" s="13" t="s">
+      <c r="D25" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="E25" s="12" t="s">
+      <c r="E25" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="F25" s="12" t="s">
+      <c r="F25" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="G25" s="20" t="s">
+      <c r="G25" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="H25" s="24" t="s">
+      <c r="H25" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="I25" s="16" t="s">
+      <c r="I25" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="J25" s="12" t="s">
+      <c r="J25" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="K25" s="17" t="s">
+      <c r="K25" s="13" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="4">
-        <v>25.0</v>
-      </c>
-      <c r="B26" s="5" t="s">
+    <row r="26" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <v>25</v>
+      </c>
+      <c r="B26" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="D26" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="E26" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="F26" s="6" t="s">
+      <c r="F26" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="G26" s="7" t="s">
+      <c r="G26" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="H26" s="23" t="s">
+      <c r="H26" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="I26" s="9" t="s">
+      <c r="I26" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="J26" s="5" t="s">
+      <c r="J26" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="K26" s="10" t="s">
+      <c r="K26" s="7" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="11">
-        <v>26.0</v>
-      </c>
-      <c r="B27" s="12" t="s">
+    <row r="27" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A27" s="8">
+        <v>26</v>
+      </c>
+      <c r="B27" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="C27" s="12" t="s">
+      <c r="C27" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D27" s="12" t="s">
+      <c r="D27" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="E27" s="12" t="s">
+      <c r="E27" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="F27" s="13" t="s">
+      <c r="F27" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="G27" s="20" t="s">
+      <c r="G27" s="15" t="s">
         <v>208</v>
       </c>
-      <c r="H27" s="24" t="s">
+      <c r="H27" s="9" t="s">
         <v>209</v>
       </c>
-      <c r="I27" s="16" t="s">
+      <c r="I27" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="J27" s="12" t="s">
+      <c r="J27" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="K27" s="17" t="s">
+      <c r="K27" s="13" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="4">
-        <v>27.0</v>
-      </c>
-      <c r="B28" s="5" t="s">
+    <row r="28" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
+        <v>27</v>
+      </c>
+      <c r="B28" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="D28" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="E28" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="F28" s="6" t="s">
+      <c r="F28" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="G28" s="7" t="s">
+      <c r="G28" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="H28" s="25" t="s">
+      <c r="H28" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="I28" s="9" t="s">
+      <c r="I28" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="J28" s="5" t="s">
+      <c r="J28" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="K28" s="19" t="s">
+      <c r="K28" s="7" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="11">
-        <v>28.0</v>
-      </c>
-      <c r="B29" s="12" t="s">
+    <row r="29" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A29" s="8">
+        <v>28</v>
+      </c>
+      <c r="B29" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="C29" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D29" s="13" t="s">
+      <c r="D29" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="E29" s="12" t="s">
+      <c r="E29" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="F29" s="13" t="s">
+      <c r="F29" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="G29" s="20" t="s">
+      <c r="G29" s="15" t="s">
         <v>223</v>
       </c>
-      <c r="H29" s="24" t="s">
+      <c r="H29" s="9" t="s">
         <v>224</v>
       </c>
-      <c r="I29" s="16" t="s">
+      <c r="I29" s="12" t="s">
         <v>225</v>
       </c>
-      <c r="J29" s="12" t="s">
+      <c r="J29" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="K29" s="17" t="s">
+      <c r="K29" s="13" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="4">
-        <v>29.0</v>
-      </c>
-      <c r="B30" s="5" t="s">
+    <row r="30" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
+        <v>29</v>
+      </c>
+      <c r="B30" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="D30" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="E30" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="F30" s="6" t="s">
+      <c r="F30" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="G30" s="7" t="s">
+      <c r="G30" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="H30" s="23" t="s">
+      <c r="H30" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="I30" s="9" t="s">
+      <c r="I30" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="J30" s="5" t="s">
+      <c r="J30" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="K30" s="19" t="s">
+      <c r="K30" s="7" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="11">
-        <v>30.0</v>
-      </c>
-      <c r="B31" s="12" t="s">
+    <row r="31" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A31" s="8">
+        <v>30</v>
+      </c>
+      <c r="B31" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="C31" s="12" t="s">
+      <c r="C31" s="9" t="s">
         <v>229</v>
       </c>
-      <c r="D31" s="12" t="s">
+      <c r="D31" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="E31" s="12" t="s">
+      <c r="E31" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="F31" s="13" t="s">
+      <c r="F31" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="G31" s="20" t="s">
+      <c r="G31" s="15" t="s">
         <v>238</v>
       </c>
-      <c r="H31" s="24" t="s">
+      <c r="H31" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="I31" s="27" t="s">
+      <c r="I31" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="J31" s="12" t="s">
+      <c r="J31" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="K31" s="17" t="s">
+      <c r="K31" s="13" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="4">
-        <v>31.0</v>
-      </c>
-      <c r="B32" s="5" t="s">
+    <row r="32" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A32" s="3">
+        <v>31</v>
+      </c>
+      <c r="B32" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="D32" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="E32" s="5" t="s">
+      <c r="E32" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="F32" s="5" t="s">
+      <c r="F32" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G32" s="7" t="s">
+      <c r="G32" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="H32" s="23" t="s">
+      <c r="H32" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="I32" s="9" t="s">
+      <c r="I32" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="J32" s="5" t="s">
+      <c r="J32" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="K32" s="19" t="s">
+      <c r="K32" s="7" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="11">
-        <v>32.0</v>
-      </c>
-      <c r="B33" s="12" t="s">
+    <row r="33" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A33" s="8">
+        <v>32</v>
+      </c>
+      <c r="B33" s="9" t="s">
         <v>249</v>
       </c>
-      <c r="C33" s="12" t="s">
+      <c r="C33" s="9" t="s">
         <v>229</v>
       </c>
-      <c r="D33" s="13" t="s">
+      <c r="D33" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="E33" s="12" t="s">
+      <c r="E33" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="F33" s="13" t="s">
+      <c r="F33" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="G33" s="20" t="s">
+      <c r="G33" s="15" t="s">
         <v>250</v>
       </c>
-      <c r="H33" s="24" t="s">
+      <c r="H33" s="9" t="s">
         <v>251</v>
       </c>
-      <c r="I33" s="16" t="s">
+      <c r="I33" s="12" t="s">
         <v>252</v>
       </c>
-      <c r="J33" s="12" t="s">
+      <c r="J33" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="K33" s="17" t="s">
+      <c r="K33" s="13" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="4">
-        <v>33.0</v>
-      </c>
-      <c r="B34" s="5" t="s">
+    <row r="34" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
+        <v>33</v>
+      </c>
+      <c r="B34" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D34" s="6" t="s">
+      <c r="D34" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="E34" s="5" t="s">
+      <c r="E34" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="F34" s="6" t="s">
+      <c r="F34" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="G34" s="7" t="s">
+      <c r="G34" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="H34" s="23" t="s">
+      <c r="H34" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="I34" s="9" t="s">
+      <c r="I34" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="J34" s="5" t="s">
+      <c r="J34" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="K34" s="10" t="s">
+      <c r="K34" s="7" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="11">
-        <v>34.0</v>
-      </c>
-      <c r="B35" s="12" t="s">
+    <row r="35" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A35" s="8">
+        <v>34</v>
+      </c>
+      <c r="B35" s="9" t="s">
         <v>262</v>
       </c>
-      <c r="C35" s="12" t="s">
+      <c r="C35" s="9" t="s">
         <v>263</v>
       </c>
-      <c r="D35" s="13" t="s">
+      <c r="D35" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="E35" s="12" t="s">
+      <c r="E35" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="F35" s="13" t="s">
+      <c r="F35" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="G35" s="20" t="s">
+      <c r="G35" s="15" t="s">
         <v>266</v>
       </c>
-      <c r="H35" s="24" t="s">
+      <c r="H35" s="9" t="s">
         <v>267</v>
       </c>
-      <c r="I35" s="16" t="s">
+      <c r="I35" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="J35" s="12" t="s">
+      <c r="J35" s="9" t="s">
         <v>269</v>
       </c>
-      <c r="K35" s="28" t="s">
+      <c r="K35" s="13" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="4">
-        <v>35.0</v>
-      </c>
-      <c r="B36" s="5" t="s">
+    <row r="36" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A36" s="3">
+        <v>35</v>
+      </c>
+      <c r="B36" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C36" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="D36" s="6" t="s">
+      <c r="D36" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="E36" s="5" t="s">
+      <c r="E36" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="F36" s="5" t="s">
+      <c r="F36" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="G36" s="7" t="s">
+      <c r="G36" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="H36" s="23" t="s">
+      <c r="H36" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="I36" s="9" t="s">
+      <c r="I36" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="J36" s="5" t="s">
+      <c r="J36" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="K36" s="10" t="s">
+      <c r="K36" s="7" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="11">
-        <v>36.0</v>
-      </c>
-      <c r="B37" s="12" t="s">
+    <row r="37" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A37" s="8">
+        <v>36</v>
+      </c>
+      <c r="B37" s="9" t="s">
         <v>279</v>
       </c>
-      <c r="C37" s="12" t="s">
+      <c r="C37" s="9" t="s">
         <v>280</v>
       </c>
-      <c r="D37" s="13" t="s">
+      <c r="D37" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="E37" s="12" t="s">
+      <c r="E37" s="9" t="s">
         <v>281</v>
       </c>
-      <c r="F37" s="13" t="s">
+      <c r="F37" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="G37" s="20" t="s">
+      <c r="G37" s="15" t="s">
         <v>282</v>
       </c>
-      <c r="H37" s="21" t="s">
+      <c r="H37" s="9" t="s">
         <v>283</v>
       </c>
-      <c r="I37" s="16" t="s">
+      <c r="I37" s="12" t="s">
         <v>284</v>
       </c>
-      <c r="J37" s="12" t="s">
+      <c r="J37" s="9" t="s">
         <v>285</v>
       </c>
-      <c r="K37" s="26" t="s">
+      <c r="K37" s="13" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="4">
-        <v>37.0</v>
-      </c>
-      <c r="B38" s="5" t="s">
+    <row r="38" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A38" s="3">
+        <v>37</v>
+      </c>
+      <c r="B38" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="C38" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="D38" s="6" t="s">
+      <c r="D38" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E38" s="5" t="s">
+      <c r="E38" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="F38" s="6" t="s">
+      <c r="F38" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G38" s="7" t="s">
+      <c r="G38" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="H38" s="6" t="s">
+      <c r="H38" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="I38" s="9" t="s">
+      <c r="I38" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="J38" s="5" t="s">
+      <c r="J38" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="K38" s="19" t="s">
+      <c r="K38" s="7" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="11">
-        <v>38.0</v>
-      </c>
-      <c r="B39" s="12" t="s">
+    <row r="39" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A39" s="8">
+        <v>38</v>
+      </c>
+      <c r="B39" s="9" t="s">
         <v>294</v>
       </c>
-      <c r="C39" s="12" t="s">
+      <c r="C39" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D39" s="13" t="s">
+      <c r="D39" s="9" t="s">
         <v>295</v>
       </c>
-      <c r="E39" s="12" t="s">
+      <c r="E39" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="F39" s="13" t="s">
+      <c r="F39" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="G39" s="20" t="s">
+      <c r="G39" s="15" t="s">
         <v>297</v>
       </c>
-      <c r="H39" s="21" t="s">
+      <c r="H39" s="9" t="s">
         <v>298</v>
       </c>
-      <c r="I39" s="16" t="s">
+      <c r="I39" s="12" t="s">
         <v>299</v>
       </c>
-      <c r="J39" s="12" t="s">
+      <c r="J39" s="9" t="s">
         <v>300</v>
       </c>
-      <c r="K39" s="26" t="s">
+      <c r="K39" s="13" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="4">
-        <v>39.0</v>
-      </c>
-      <c r="B40" s="5" t="s">
+    <row r="40" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A40" s="3">
+        <v>39</v>
+      </c>
+      <c r="B40" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C40" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D40" s="6" t="s">
+      <c r="D40" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E40" s="5" t="s">
+      <c r="E40" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="F40" s="6" t="s">
+      <c r="F40" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="G40" s="7" t="s">
+      <c r="G40" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="H40" s="5" t="s">
+      <c r="H40" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="I40" s="9" t="s">
+      <c r="I40" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="J40" s="5" t="s">
+      <c r="J40" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="K40" s="29" t="s">
+      <c r="K40" s="18" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="11">
-        <v>40.0</v>
-      </c>
-      <c r="B41" s="12" t="s">
+    <row r="41" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A41" s="8">
+        <v>40</v>
+      </c>
+      <c r="B41" s="9" t="s">
         <v>307</v>
       </c>
-      <c r="C41" s="12" t="s">
+      <c r="C41" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D41" s="13" t="s">
+      <c r="D41" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E41" s="12" t="s">
+      <c r="E41" s="9" t="s">
         <v>308</v>
       </c>
-      <c r="F41" s="13" t="s">
+      <c r="F41" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="G41" s="20" t="s">
+      <c r="G41" s="15" t="s">
         <v>309</v>
       </c>
-      <c r="H41" s="13" t="s">
+      <c r="H41" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="I41" s="16" t="s">
+      <c r="I41" s="12" t="s">
         <v>310</v>
       </c>
-      <c r="J41" s="12" t="s">
+      <c r="J41" s="9" t="s">
         <v>311</v>
       </c>
-      <c r="K41" s="30" t="s">
+      <c r="K41" s="19" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="4">
-        <v>41.0</v>
-      </c>
-      <c r="B42" s="5" t="s">
+    <row r="42" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A42" s="3">
+        <v>41</v>
+      </c>
+      <c r="B42" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="C42" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D42" s="6" t="s">
+      <c r="D42" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="E42" s="5" t="s">
+      <c r="E42" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="F42" s="6" t="s">
+      <c r="F42" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="G42" s="7" t="s">
+      <c r="G42" s="5" t="s">
         <v>316</v>
       </c>
-      <c r="H42" s="6" t="s">
+      <c r="H42" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="I42" s="9" t="s">
+      <c r="I42" s="6" t="s">
         <v>318</v>
       </c>
-      <c r="J42" s="5" t="s">
+      <c r="J42" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="K42" s="19" t="s">
+      <c r="K42" s="7" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="11">
-        <v>42.0</v>
-      </c>
-      <c r="B43" s="12" t="s">
+    <row r="43" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A43" s="8">
+        <v>42</v>
+      </c>
+      <c r="B43" s="9" t="s">
         <v>321</v>
       </c>
-      <c r="C43" s="12" t="s">
+      <c r="C43" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D43" s="13" t="s">
+      <c r="D43" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E43" s="12" t="s">
+      <c r="E43" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="F43" s="12" t="s">
+      <c r="F43" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="G43" s="20" t="s">
+      <c r="G43" s="15" t="s">
         <v>322</v>
       </c>
-      <c r="H43" s="13" t="s">
+      <c r="H43" s="9" t="s">
         <v>323</v>
       </c>
-      <c r="I43" s="16" t="s">
+      <c r="I43" s="12" t="s">
         <v>324</v>
       </c>
-      <c r="J43" s="12" t="s">
+      <c r="J43" s="9" t="s">
         <v>325</v>
       </c>
-      <c r="K43" s="30" t="s">
+      <c r="K43" s="19" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="4">
-        <v>43.0</v>
-      </c>
-      <c r="B44" s="5" t="s">
+    <row r="44" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A44" s="3">
+        <v>43</v>
+      </c>
+      <c r="B44" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="C44" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D44" s="6" t="s">
+      <c r="D44" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E44" s="5" t="s">
+      <c r="E44" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="F44" s="6" t="s">
+      <c r="F44" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="G44" s="7" t="s">
+      <c r="G44" s="5" t="s">
         <v>329</v>
       </c>
-      <c r="H44" s="5" t="s">
+      <c r="H44" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="I44" s="9" t="s">
+      <c r="I44" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J44" s="5" t="s">
+      <c r="J44" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="K44" s="29" t="s">
+      <c r="K44" s="18" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="11">
-        <v>44.0</v>
-      </c>
-      <c r="B45" s="12" t="s">
+    <row r="45" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A45" s="8">
+        <v>44</v>
+      </c>
+      <c r="B45" s="9" t="s">
         <v>334</v>
       </c>
-      <c r="C45" s="12" t="s">
+      <c r="C45" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D45" s="13" t="s">
+      <c r="D45" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E45" s="12" t="s">
+      <c r="E45" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="F45" s="13" t="s">
+      <c r="F45" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="G45" s="20" t="s">
+      <c r="G45" s="15" t="s">
         <v>335</v>
       </c>
-      <c r="H45" s="12" t="s">
+      <c r="H45" s="9" t="s">
         <v>336</v>
       </c>
-      <c r="I45" s="16" t="s">
+      <c r="I45" s="12" t="s">
         <v>337</v>
       </c>
-      <c r="J45" s="12" t="s">
+      <c r="J45" s="9" t="s">
         <v>338</v>
       </c>
-      <c r="K45" s="30" t="s">
+      <c r="K45" s="19" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="4">
-        <v>45.0</v>
-      </c>
-      <c r="B46" s="5" t="s">
+    <row r="46" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A46" s="3">
+        <v>45</v>
+      </c>
+      <c r="B46" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="C46" s="5" t="s">
+      <c r="C46" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="D46" s="6" t="s">
+      <c r="D46" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="E46" s="5" t="s">
+      <c r="E46" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="F46" s="6" t="s">
+      <c r="F46" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="G46" s="7" t="s">
+      <c r="G46" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="H46" s="5" t="s">
+      <c r="H46" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="I46" s="9" t="s">
+      <c r="I46" s="6" t="s">
         <v>345</v>
       </c>
-      <c r="J46" s="5" t="s">
+      <c r="J46" s="4" t="s">
         <v>346</v>
       </c>
-      <c r="K46" s="29" t="s">
+      <c r="K46" s="18" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="11">
-        <v>46.0</v>
-      </c>
-      <c r="B47" s="12" t="s">
+    <row r="47" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A47" s="8">
+        <v>46</v>
+      </c>
+      <c r="B47" s="9" t="s">
         <v>348</v>
       </c>
-      <c r="C47" s="12" t="s">
+      <c r="C47" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D47" s="13" t="s">
+      <c r="D47" s="9" t="s">
         <v>349</v>
       </c>
-      <c r="E47" s="12" t="s">
+      <c r="E47" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="F47" s="13" t="s">
+      <c r="F47" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="G47" s="20" t="s">
+      <c r="G47" s="15" t="s">
         <v>350</v>
       </c>
-      <c r="H47" s="12" t="s">
+      <c r="H47" s="9" t="s">
         <v>351</v>
       </c>
-      <c r="I47" s="16" t="s">
+      <c r="I47" s="12" t="s">
         <v>352</v>
       </c>
-      <c r="J47" s="12" t="s">
+      <c r="J47" s="9" t="s">
         <v>353</v>
       </c>
-      <c r="K47" s="30" t="s">
+      <c r="K47" s="19" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="4">
-        <v>47.0</v>
-      </c>
-      <c r="B48" s="5" t="s">
+    <row r="48" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A48" s="3">
+        <v>47</v>
+      </c>
+      <c r="B48" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="C48" s="5" t="s">
+      <c r="C48" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D48" s="6" t="s">
+      <c r="D48" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E48" s="5" t="s">
+      <c r="E48" s="4" t="s">
         <v>356</v>
       </c>
-      <c r="F48" s="5" t="s">
+      <c r="F48" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G48" s="7" t="s">
+      <c r="G48" s="5" t="s">
         <v>357</v>
       </c>
-      <c r="H48" s="31" t="s">
+      <c r="H48" s="20" t="s">
         <v>358</v>
       </c>
-      <c r="I48" s="9" t="s">
+      <c r="I48" s="6" t="s">
         <v>359</v>
       </c>
-      <c r="J48" s="5" t="s">
+      <c r="J48" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="K48" s="29" t="s">
+      <c r="K48" s="18" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="11">
-        <v>48.0</v>
-      </c>
-      <c r="B49" s="12" t="s">
+    <row r="49" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A49" s="8">
+        <v>48</v>
+      </c>
+      <c r="B49" s="9" t="s">
         <v>362</v>
       </c>
-      <c r="C49" s="12" t="s">
+      <c r="C49" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D49" s="13" t="s">
+      <c r="D49" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E49" s="12" t="s">
+      <c r="E49" s="9" t="s">
         <v>363</v>
       </c>
-      <c r="F49" s="13" t="s">
+      <c r="F49" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="G49" s="20" t="s">
+      <c r="G49" s="15" t="s">
         <v>364</v>
       </c>
-      <c r="H49" s="13" t="s">
+      <c r="H49" s="9" t="s">
         <v>365</v>
       </c>
-      <c r="I49" s="16" t="s">
+      <c r="I49" s="12" t="s">
         <v>366</v>
       </c>
-      <c r="J49" s="12" t="s">
+      <c r="J49" s="9" t="s">
         <v>367</v>
       </c>
-      <c r="K49" s="30" t="s">
+      <c r="K49" s="19" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="4">
-        <v>49.0</v>
-      </c>
-      <c r="B50" s="5" t="s">
+    <row r="50" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A50" s="3">
+        <v>49</v>
+      </c>
+      <c r="B50" s="4" t="s">
         <v>369</v>
       </c>
-      <c r="C50" s="5" t="s">
+      <c r="C50" s="4" t="s">
         <v>370</v>
       </c>
-      <c r="D50" s="6" t="s">
+      <c r="D50" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E50" s="5" t="s">
+      <c r="E50" s="4" t="s">
         <v>371</v>
       </c>
-      <c r="F50" s="6" t="s">
+      <c r="F50" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="G50" s="7" t="s">
+      <c r="G50" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="H50" s="5" t="s">
+      <c r="H50" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="I50" s="9" t="s">
+      <c r="I50" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="J50" s="5" t="s">
+      <c r="J50" s="4" t="s">
         <v>375</v>
       </c>
-      <c r="K50" s="19" t="s">
+      <c r="K50" s="7" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="32">
-        <v>50.0</v>
-      </c>
-      <c r="B51" s="33" t="s">
+    <row r="51" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A51" s="21">
+        <v>50</v>
+      </c>
+      <c r="B51" s="22" t="s">
         <v>377</v>
       </c>
-      <c r="C51" s="33" t="s">
+      <c r="C51" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="D51" s="34" t="s">
+      <c r="D51" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="E51" s="33" t="s">
+      <c r="E51" s="22" t="s">
         <v>273</v>
       </c>
-      <c r="F51" s="34" t="s">
+      <c r="F51" s="22" t="s">
         <v>342</v>
       </c>
-      <c r="G51" s="35" t="s">
+      <c r="G51" s="23" t="s">
         <v>378</v>
       </c>
-      <c r="H51" s="36" t="s">
+      <c r="H51" s="22" t="s">
         <v>379</v>
       </c>
-      <c r="I51" s="37" t="s">
+      <c r="I51" s="24" t="s">
         <v>380</v>
       </c>
-      <c r="J51" s="33" t="s">
+      <c r="J51" s="22" t="s">
         <v>285</v>
       </c>
-      <c r="K51" s="38" t="s">
+      <c r="K51" s="25" t="s">
         <v>381</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="G2"/>
-    <hyperlink r:id="rId2" ref="K2"/>
-    <hyperlink r:id="rId3" ref="G3"/>
-    <hyperlink r:id="rId4" ref="G4"/>
-    <hyperlink r:id="rId5" ref="H4"/>
-    <hyperlink r:id="rId6" ref="G5"/>
-    <hyperlink r:id="rId7" ref="G6"/>
-    <hyperlink r:id="rId8" ref="G7"/>
-    <hyperlink r:id="rId9" ref="G8"/>
-    <hyperlink r:id="rId10" ref="K8"/>
-    <hyperlink r:id="rId11" ref="G9"/>
-    <hyperlink r:id="rId12" ref="G10"/>
-    <hyperlink r:id="rId13" ref="G11"/>
-    <hyperlink r:id="rId14" ref="G12"/>
-    <hyperlink r:id="rId15" ref="G13"/>
-    <hyperlink r:id="rId16" ref="G14"/>
-    <hyperlink r:id="rId17" ref="G15"/>
-    <hyperlink r:id="rId18" ref="K15"/>
-    <hyperlink r:id="rId19" ref="G16"/>
-    <hyperlink r:id="rId20" ref="G17"/>
-    <hyperlink r:id="rId21" ref="G18"/>
-    <hyperlink r:id="rId22" ref="G19"/>
-    <hyperlink r:id="rId23" ref="G20"/>
-    <hyperlink r:id="rId24" ref="G21"/>
-    <hyperlink r:id="rId25" ref="G22"/>
-    <hyperlink r:id="rId26" ref="G23"/>
-    <hyperlink r:id="rId27" ref="G24"/>
-    <hyperlink r:id="rId28" ref="G25"/>
-    <hyperlink r:id="rId29" ref="G26"/>
-    <hyperlink r:id="rId30" ref="K26"/>
-    <hyperlink r:id="rId31" ref="G27"/>
-    <hyperlink r:id="rId32" ref="G28"/>
-    <hyperlink r:id="rId33" ref="G29"/>
-    <hyperlink r:id="rId34" ref="G30"/>
-    <hyperlink r:id="rId35" ref="G31"/>
-    <hyperlink r:id="rId36" ref="G32"/>
-    <hyperlink r:id="rId37" ref="G33"/>
-    <hyperlink r:id="rId38" ref="G34"/>
-    <hyperlink r:id="rId39" ref="K34"/>
-    <hyperlink r:id="rId40" ref="G35"/>
-    <hyperlink r:id="rId41" ref="K35"/>
-    <hyperlink r:id="rId42" ref="G36"/>
-    <hyperlink r:id="rId43" ref="K36"/>
-    <hyperlink r:id="rId44" ref="G37"/>
-    <hyperlink r:id="rId45" ref="K37"/>
-    <hyperlink r:id="rId46" ref="G38"/>
-    <hyperlink r:id="rId47" ref="G39"/>
-    <hyperlink r:id="rId48" ref="K39"/>
-    <hyperlink r:id="rId49" ref="G40"/>
-    <hyperlink r:id="rId50" ref="K40"/>
-    <hyperlink r:id="rId51" ref="G41"/>
-    <hyperlink r:id="rId52" ref="K41"/>
-    <hyperlink r:id="rId53" ref="G42"/>
-    <hyperlink r:id="rId54" ref="G43"/>
-    <hyperlink r:id="rId55" ref="K43"/>
-    <hyperlink r:id="rId56" ref="G44"/>
-    <hyperlink r:id="rId57" ref="K44"/>
-    <hyperlink r:id="rId58" ref="G45"/>
-    <hyperlink r:id="rId59" ref="K45"/>
-    <hyperlink r:id="rId60" ref="G46"/>
-    <hyperlink r:id="rId61" ref="K46"/>
-    <hyperlink r:id="rId62" ref="G47"/>
-    <hyperlink r:id="rId63" ref="K47"/>
-    <hyperlink r:id="rId64" ref="G48"/>
-    <hyperlink r:id="rId65" ref="K48"/>
-    <hyperlink r:id="rId66" ref="G49"/>
-    <hyperlink r:id="rId67" ref="K49"/>
-    <hyperlink r:id="rId68" ref="G50"/>
-    <hyperlink r:id="rId69" ref="G51"/>
-    <hyperlink r:id="rId70" ref="H51"/>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="K2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="G3" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="G4" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="H4" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="G5" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="G6" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="G7" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="G8" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="K8" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="G9" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="G10" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="G11" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="G12" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="G13" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="G14" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="G15" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="K15" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="G16" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="G17" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="G18" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="G19" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="G20" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="G21" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="G22" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="G23" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="G24" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="G25" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="G26" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="K26" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="G27" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="G28" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="G29" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="G30" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="G31" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="G32" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="G33" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="G34" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="K34" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="G35" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="K35" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="G36" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="K36" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="G37" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="K37" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="G38" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="G39" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="K39" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="G40" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="K40" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="G41" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="K41" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="G42" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="G43" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="K43" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="G44" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="K44" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="G45" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="K45" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="G46" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="K46" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="G47" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="K47" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="G48" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="K48" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="G49" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="K49" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="G50" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="G51" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="H51" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
   </hyperlinks>
-  <drawing r:id="rId71"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId73"/>
+    <tablePart r:id="rId71"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetData/>
-  <sheetProtection objects="1" selectLockedCells="1" selectUnlockedCells="1" sheet="1"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
-  <sheetData/>
-  <drawing r:id="rId1"/>
-</worksheet>
 </file>